--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="252">
   <si>
     <t>№</t>
   </si>
@@ -564,127 +564,229 @@
     <t>3. Селекторы data-test не генерируются динамически, остаются стабильными"</t>
   </si>
   <si>
-    <t>1. Пользователь зарегистрирован в системе / 2. Пользователь находится на форме авторизации</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» зарегистрированное имя пользователя / 2. Ввести в поле «Password» верный пароль / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Значение отображается корректно. Ошибок валидации нет / 2. Значение маскируется точками (символы скрыты) / 3. Происходит перенаправление на страницу со списком продуктов. В шапке сайта отображается имя пользователя. В браузере сохраняются сессионные куки</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» зарегистрированное имя пользователя / 2. Ввести в поле «Password» неверный пароль / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Значение отображается корректно. Ошибок валидации нет / 2. Значение маскируется точками (символы скрыты) / 3. Пользователь остается на странице авторизации. Поля ввода подчеркиваются красным. Появляется сообщение об ошибке: «Epic sadface: Username and password do not match any user in this service». Авторизация не выполнена</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» locked_out_user / 2. Ввести в поле «Password» secret_sauce / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Форма мгновенно блокируется / 2. Появляется ошибка: «Epic sadface: Sorry, this user has been locked out.»</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» problem_user / 2. Ввести в поле «Password» secret_sauce / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Вход выполнен / 2. В каталоге пути к картинкам товаров некорректны / 3. Часть кнопок «Add to cart» не работает</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» performance_glitch_user / 2. Ввести в поле «Password» secret_sauce / 3. Нажать кнопку «Войти» и замерить время ответа</t>
-  </si>
-  <si>
-    <t>1. Ответ сервера задерживается примерно на 5000 мс / 2. После задержки — успешный вход</t>
-  </si>
-  <si>
-    <t>1. Оставить поле «Username» пустым / 2. Ввести в поле «Password» secret_sauce / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Ввести в поле «Username» standard_user / 2. Оставить поле «Password» пустым / 3. Нажать кнопку «Войти»</t>
-  </si>
-  <si>
-    <t>1. Перенаправление на главную страницу / 2. Ошибка: «Epic sadface: You can only access '/inventory.html' after logging in.»</t>
-  </si>
-  <si>
-    <t>1. Ввести Username длиной 1 символ / 2. Ввести Username длиной 50 символов / 3. Ввести Username длиной 51 символ / 4. Проверить чувствительность к регистру</t>
-  </si>
-  <si>
-    <t>1. 1 символ — принимается / 2. 50 символов — принимается / 3. 51 символ — не принимается / 4. Регистр учитывается</t>
-  </si>
-  <si>
-    <t>1. Проверить кнопку товара по умолчанию / 2. Нажать «Add to cart» / 3. Перейти на страницу товара (Product Details) / 4. Вернуться в каталог</t>
-  </si>
-  <si>
-    <t>1. Отображается «Add to cart» (тёмно-серый/чёрный текст) / 2. Кнопка мгновенно меняется на «Remove» (красный текст) / 3. Кнопка сохраняет состояние «Remove» / 4. Состояние «Remove» сохранено</t>
-  </si>
-  <si>
-    <t>1. Выбрать «Name (A to Z)» / 2. Выбрать «Name (Z to A)»</t>
-  </si>
-  <si>
-    <t>1. Товары отсортированы по английскому алфавиту (A→Z) / 2. Товары отсортированы по английскому алфавиту (Z→A)</t>
-  </si>
-  <si>
-    <t>1. Выбрать «Price (low to high)» / 2. Выбрать «Price (high to low)»</t>
-  </si>
-  <si>
-    <t>1. Товары отсортированы по числовому значению цены (без учёта $) по возрастанию / 2. Товары отсортированы по убыванию</t>
-  </si>
-  <si>
-    <t>1. Корзина пуста / 2. Добавить 1 товар / 3. Добавить товары до 6 / 4. Удалить товар / 5. Удалить все товары</t>
-  </si>
-  <si>
-    <t>1. Индикатор скрыт / не отображает 0 / 2. Счётчик = 1 / 3. Счётчик корректно отображает 1–6 / 4. Счётчик уменьшается на 1 / 5. Счётчик скрывается</t>
-  </si>
-  <si>
-    <t>1. Добавить товары в корзину / 2. Изменить порядок сортировки в каталоге / 3. Перейти в /cart.html</t>
-  </si>
-  <si>
-    <t>1. Товары добавлены / 2. Порядок в корзине не меняется / 3. Для каждого товара отображаются точное наименование, описание и цена на момент добавления</t>
-  </si>
-  <si>
-    <t>1. В корзине есть товары / 2. Пользователь на странице оформления</t>
-  </si>
-  <si>
-    <t>1. Оставить все поля пустыми, нажать «Continue» / 2. Заполнить First Name, остальные пустые, нажать «Continue» / 3. Заполнить First Name, Last Name, Postal Code пустой, нажать «Continue» / 4. Ввести значения с пробелами в начале и конце</t>
-  </si>
-  <si>
-    <t>1. Ошибка: «Error: First Name is required» / 2. Ошибка: «Error: Last Name is required» / 3. Ошибка: «Error: Postal Code is required» / 4. Пробелы обрезаются (trimming)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> переход на Overview</t>
-  </si>
-  <si>
-    <t>1. В корзине есть товары / 2. Форма «Your Information» заполнена</t>
-  </si>
-  <si>
-    <t>1. Проверить Item total / 2. Проверить Tax / 3. Проверить Total</t>
-  </si>
-  <si>
-    <t>1. Сумма цен всех товаров, округление до 2 знаков / 2. 8% от Item total, рассчитан автоматически / 3. Строго Item total + Tax</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ошибка округления недопустима</t>
-  </si>
-  <si>
-    <t>1. Пользователь авторизован / 2. В корзине есть товары / 3. Выбрана сортировка, отличная от «A to Z»</t>
-  </si>
-  <si>
-    <t>1. Нажать «Reset App State» / 2. Проверить счётчик / 3. Проверить кнопки товаров / 4. Проверить фильтр сортировки / 5. Убедиться в отсутствии перезагрузки</t>
-  </si>
-  <si>
-    <t>1. Все товары удалены из корзины / 2. Счётчик сброшен / скрыт / 3. Все кнопки в статусе «Add to cart» / 4. Фильтр сброшен на «A to Z» / 5. Изменения мгновенные, без F5</t>
-  </si>
-  <si>
-    <t>1. Авторизоваться / 2. Нажать «Logout» / 3. Нажать «Назад» в браузере</t>
-  </si>
-  <si>
-    <t>1. Сессия сохранена (cookies / sessionStorage) / 2. Токен/сессия уничтожены / 3. Доступ к каталогу не предоставляется</t>
-  </si>
-  <si>
-    <t>1. Проверить поле ввода имени / 2. Проверить кнопку завершения заказа / 3. Перезагрузить страницу</t>
-  </si>
-  <si>
-    <t>1. &lt;input data-test="firstName" .../&gt; / 2. &lt;button data-test="finish" .../&gt; / 3. Селекторы data-test не генерируются динамически, остаются стабильными</t>
+    <t>1. Ввести в поле «Username» зарегистрированное имя пользователя</t>
+  </si>
+  <si>
+    <t>3. Нажать кнопку «Войти»</t>
+  </si>
+  <si>
+    <t>1. Значение отображается корректно. Ошибок валидации нет</t>
+  </si>
+  <si>
+    <t>3. Происходит перенаправление на страницу со списком продуктов. В шапке сайта отображается имя пользователя. В браузере сохраняются сессионные куки</t>
+  </si>
+  <si>
+    <t>3. Пользователь остается на странице авторизации. Поля ввода подчеркиваются красным. Появляется сообщение об ошибке: «Epic sadface: Username and password do not match any user in this service». Авторизация не выполнена</t>
+  </si>
+  <si>
+    <t>1. Пользователь зарегистрирован в системе</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. Пользователь находится на форме авторизации</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ввести в поле «Username» locked_out_user </t>
+  </si>
+  <si>
+    <t>1. Форма мгновенно блокируется</t>
+  </si>
+  <si>
+    <t>2. Появляется ошибка: «Epic sadface: Sorry, this user has been locked out.»</t>
+  </si>
+  <si>
+    <t>1. Ввести в поле «Username» problem_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. В каталоге пути к картинкам товаров некорректны</t>
+  </si>
+  <si>
+    <t>1. Вход выполнен</t>
+  </si>
+  <si>
+    <t>3. Часть кнопок «Add to cart» не работает</t>
+  </si>
+  <si>
+    <t>3. Нажать кнопку «Войти» и замерить время ответа</t>
+  </si>
+  <si>
+    <t>1. Ввести в поле «Username» performance_glitch_user</t>
+  </si>
+  <si>
+    <t>1. Ответ сервера задерживается примерно на 5000 мс</t>
+  </si>
+  <si>
+    <t>2. После задержки — успешный вход</t>
+  </si>
+  <si>
+    <t>1. Оставить поле «Username» пустым</t>
+  </si>
+  <si>
+    <t>1. В корзине есть товары</t>
+  </si>
+  <si>
+    <t>2. Пользователь на странице оформления</t>
+  </si>
+  <si>
+    <t>2. Форма «Your Information» заполнена</t>
+  </si>
+  <si>
+    <t>1. Ввести в поле «Username» standard_user</t>
+  </si>
+  <si>
+    <t>1. Перенаправление на главную страницу</t>
+  </si>
+  <si>
+    <t>2. Ошибка: «Epic sadface: You can only access '/inventory.html' after logging in.»</t>
+  </si>
+  <si>
+    <t>4. Регистр учитывается</t>
+  </si>
+  <si>
+    <t>1. 1 символ — принимается</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Ввести Username длиной 51 символ </t>
+  </si>
+  <si>
+    <t>1. Ввести Username длиной 1 символ</t>
+  </si>
+  <si>
+    <t>4. Проверить чувствительность к регистру</t>
+  </si>
+  <si>
+    <t>1. Проверить кнопку товара по умолчанию</t>
+  </si>
+  <si>
+    <t>4. Вернуться в каталог</t>
+  </si>
+  <si>
+    <t>1. Отображается «Add to cart» (тёмно-серый/чёрный текст)</t>
+  </si>
+  <si>
+    <t>4. Состояние «Remove» сохранено</t>
+  </si>
+  <si>
+    <t>1. Выбрать «Name (A to Z)»</t>
+  </si>
+  <si>
+    <t>2. Выбрать «Name (Z to A)»</t>
+  </si>
+  <si>
+    <t>1. Товары отсортированы по английскому алфавиту (A→Z)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. Товары отсортированы по английскому алфавиту (Z→A)</t>
+  </si>
+  <si>
+    <t>2. Товары отсортированы по убыванию</t>
+  </si>
+  <si>
+    <t>1. Товары отсортированы по числовому значению цены (без учёта $) по возрастанию</t>
+  </si>
+  <si>
+    <t>1. Выбрать «Price (low to high)»</t>
+  </si>
+  <si>
+    <t>2. Выбрать «Price (high to low)»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Добавить товары до 6 </t>
+  </si>
+  <si>
+    <t>1. Корзина пуста</t>
+  </si>
+  <si>
+    <t>5. Удалить все товары</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Удалить товар </t>
+  </si>
+  <si>
+    <t>1. Индикатор скрыт / не отображает 0</t>
+  </si>
+  <si>
+    <t>5. Счётчик скрывается</t>
+  </si>
+  <si>
+    <t>3. Перезагрузить страницу</t>
+  </si>
+  <si>
+    <t>1. Проверить поле ввода имени</t>
+  </si>
+  <si>
+    <t>3. Нажать «Назад» в браузере</t>
+  </si>
+  <si>
+    <t>1. Авторизоваться</t>
+  </si>
+  <si>
+    <t>1. Нажать «Reset App State»</t>
+  </si>
+  <si>
+    <t>5. Убедиться в отсутствии перезагрузки</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. Счётчик сброшен / скрыт</t>
+  </si>
+  <si>
+    <t>1. Все товары удалены из корзины</t>
+  </si>
+  <si>
+    <t>5. Изменения мгновенные, без F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2. Токен/сессия уничтожены</t>
+  </si>
+  <si>
+    <t>1. Сессия сохранена (cookies / sessionStorage)</t>
+  </si>
+  <si>
+    <t>3. Доступ к каталогу не предоставляется</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. &lt;button data-test="finish" .../&gt; </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. &lt;input data-test="firstName" .../&gt;  </t>
+  </si>
+  <si>
+    <t>3. Селекторы data-test не генерируются динамически, остаются стабильными</t>
+  </si>
+  <si>
+    <t>1. Сумма цен всех товаров, округление до 2 знаков</t>
+  </si>
+  <si>
+    <t>3. Строго Item total + Tax</t>
+  </si>
+  <si>
+    <t>1. Ошибка: «Error: First Name is required»</t>
+  </si>
+  <si>
+    <t>4. Пробелы обрезаются (trimming)</t>
+  </si>
+  <si>
+    <t>1. Оставить все поля пустыми, нажать «Continue»</t>
+  </si>
+  <si>
+    <t>4. Ввести значения с пробелами в начале и конце</t>
+  </si>
+  <si>
+    <t>3. Перейти в /cart.html</t>
+  </si>
+  <si>
+    <t>1. Добавить товары в корзину</t>
+  </si>
+  <si>
+    <t>3. Проверить Total</t>
+  </si>
+  <si>
+    <t>1. Проверить Item total</t>
+  </si>
+  <si>
+    <t>1. Товары добавлены</t>
+  </si>
+  <si>
+    <t>3. Для каждого товара отображаются точное наименование, описание и цена на момент добавления</t>
   </si>
 </sst>
 </file>
@@ -709,7 +811,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="12">
     <border>
       <left/>
       <right/>
@@ -717,13 +819,187 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -2041,482 +2317,1135 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="9.140625" customWidth="1"/>
-    <col min="5" max="5" width="126.7109375" customWidth="1"/>
-    <col min="6" max="6" width="177.5703125" customWidth="1"/>
-    <col min="7" max="7" width="63.85546875" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="31.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="52.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="12.140625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="48.28515625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="71.140625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="84.42578125" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="17" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="1">
+    <row r="2" spans="1:7" ht="30">
+      <c r="A2" s="12">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="13"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" ht="30">
+      <c r="A4" s="14"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="9"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G4" s="11" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="12">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="G5" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="13"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="45">
+      <c r="A7" s="14"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="12">
+        <v>3</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="G8" s="5" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="13"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="14"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="9"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G10" s="19"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="12">
+        <v>4</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="13"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="14"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="9"/>
+      <c r="F13" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="12">
+        <v>5</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="13"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="14"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="10" t="s">
+        <v>191</v>
+      </c>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12">
+        <v>6</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="G17" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="13"/>
+      <c r="B18" s="6"/>
+      <c r="C18" s="6"/>
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="14"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="12">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="13"/>
+      <c r="B21" s="6"/>
+      <c r="C21" s="6"/>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="G21" s="18"/>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" s="14"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="12">
+        <v>8</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="G23" s="20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="13"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6"/>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="18"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="14"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="11" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" s="12">
+        <v>9</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="G26" s="5" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="13"/>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="G27" s="8" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28" s="13"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="7" t="s">
+        <v>204</v>
+      </c>
+      <c r="G28" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="14"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="12">
+        <v>10</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="13"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="G31" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="13"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="G32" s="8" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="14"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
+      <c r="A34" s="12">
+        <v>11</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="G34" s="5" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="14"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
+      <c r="A36" s="12">
+        <v>12</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="G36" s="5" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
+      <c r="A37" s="14"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
+      <c r="A38" s="12">
         <v>13</v>
       </c>
-      <c r="D3" t="s">
+      <c r="B38" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="G38" s="5" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="13"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="G39" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40" s="13"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G40" s="8" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41" s="13"/>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G41" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="14"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" s="12">
         <v>14</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="13"/>
+      <c r="B44" s="6"/>
+      <c r="C44" s="6"/>
+      <c r="D44" s="6"/>
+      <c r="E44" s="6"/>
+      <c r="F44" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="30">
+      <c r="A45" s="14"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" s="12">
         <v>15</v>
       </c>
-      <c r="F3" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B46" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="G46" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47" s="13"/>
+      <c r="B47" s="6"/>
+      <c r="C47" s="6"/>
+      <c r="D47" s="6"/>
+      <c r="E47" s="6"/>
+      <c r="F47" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="G47" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="13"/>
+      <c r="B48" s="6"/>
+      <c r="C48" s="6"/>
+      <c r="D48" s="6"/>
+      <c r="E48" s="6"/>
+      <c r="F48" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="G48" s="8" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="30">
+      <c r="A49" s="14"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="G49" s="11" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="12">
+        <v>16</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G50" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="13"/>
+      <c r="B51" s="6"/>
+      <c r="C51" s="6"/>
+      <c r="D51" s="6"/>
+      <c r="E51" s="6"/>
+      <c r="F51" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G51" s="8" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="30">
+      <c r="A52" s="14"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F52" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="G52" s="11" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" s="12">
+        <v>17</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="13"/>
+      <c r="B54" s="6"/>
+      <c r="C54" s="6"/>
+      <c r="D54" s="6"/>
+      <c r="E54" s="6"/>
+      <c r="F54" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G54" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="13"/>
+      <c r="B55" s="6"/>
+      <c r="C55" s="6"/>
+      <c r="D55" s="6"/>
+      <c r="E55" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="G55" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" s="13"/>
+      <c r="B56" s="6"/>
+      <c r="C56" s="6"/>
+      <c r="D56" s="6"/>
+      <c r="E56" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="G56" s="8" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="14"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58" s="12">
         <v>18</v>
       </c>
-      <c r="D4" t="s">
+      <c r="B58" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" t="s">
-        <v>182</v>
-      </c>
-      <c r="G4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="E58" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F58" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G58" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59" s="13"/>
+      <c r="B59" s="6"/>
+      <c r="C59" s="6"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="6"/>
+      <c r="F59" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="G59" s="8" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60" s="14"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="G60" s="11" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61" s="12">
+        <v>19</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E5" t="s">
-        <v>15</v>
-      </c>
-      <c r="F5" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G6" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" t="s">
-        <v>14</v>
-      </c>
-      <c r="E9" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" t="s">
-        <v>35</v>
-      </c>
-      <c r="G9" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" t="s">
-        <v>191</v>
-      </c>
-      <c r="G10" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" t="s">
-        <v>42</v>
-      </c>
-      <c r="F11" t="s">
-        <v>193</v>
-      </c>
-      <c r="G11" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
+      <c r="E61" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F12" t="s">
-        <v>195</v>
-      </c>
-      <c r="G12" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" t="s">
-        <v>46</v>
-      </c>
-      <c r="F13" t="s">
-        <v>197</v>
-      </c>
-      <c r="G13" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="1">
-        <v>13</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>53</v>
-      </c>
-      <c r="D14" t="s">
-        <v>9</v>
-      </c>
-      <c r="E14" t="s">
-        <v>46</v>
-      </c>
-      <c r="F14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G14" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
-      <c r="A15" s="1">
-        <v>14</v>
-      </c>
-      <c r="B15" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" t="s">
-        <v>46</v>
-      </c>
-      <c r="F15" t="s">
-        <v>201</v>
-      </c>
-      <c r="G15" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="A16" s="1">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" t="s">
-        <v>14</v>
-      </c>
-      <c r="E16" t="s">
-        <v>203</v>
-      </c>
-      <c r="F16" t="s">
-        <v>204</v>
-      </c>
-      <c r="G16" t="s">
-        <v>205</v>
-      </c>
-      <c r="H16" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>59</v>
-      </c>
-      <c r="C17" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" t="s">
-        <v>207</v>
-      </c>
-      <c r="F17" t="s">
-        <v>208</v>
-      </c>
-      <c r="G17" t="s">
-        <v>209</v>
-      </c>
-      <c r="H17" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
-      <c r="A18" s="1">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" t="s">
-        <v>211</v>
-      </c>
-      <c r="F18" t="s">
-        <v>212</v>
-      </c>
-      <c r="G18" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" t="s">
-        <v>72</v>
-      </c>
-      <c r="D19" t="s">
-        <v>14</v>
-      </c>
-      <c r="E19" t="s">
-        <v>46</v>
-      </c>
-      <c r="F19" t="s">
-        <v>214</v>
-      </c>
-      <c r="G19" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" t="s">
-        <v>75</v>
-      </c>
-      <c r="D20" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" t="s">
-        <v>46</v>
-      </c>
-      <c r="F20" t="s">
-        <v>216</v>
-      </c>
-      <c r="G20" t="s">
-        <v>217</v>
+      <c r="F61" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="G61" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62" s="13"/>
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+      <c r="E62" s="6"/>
+      <c r="F62" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="G62" s="8" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63" s="14"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>239</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="102">
+    <mergeCell ref="E50:E51"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D46:D49"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="C46:C49"/>
+    <mergeCell ref="D53:D57"/>
+    <mergeCell ref="E61:E63"/>
+    <mergeCell ref="D61:D63"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="E58:E60"/>
+    <mergeCell ref="E53:E54"/>
+    <mergeCell ref="E56:E57"/>
+    <mergeCell ref="B46:B49"/>
+    <mergeCell ref="B50:B52"/>
+    <mergeCell ref="B61:B63"/>
+    <mergeCell ref="B58:B60"/>
+    <mergeCell ref="B53:B57"/>
+    <mergeCell ref="C61:C63"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="C53:C57"/>
+    <mergeCell ref="B38:B42"/>
+    <mergeCell ref="E38:E42"/>
+    <mergeCell ref="E43:E45"/>
+    <mergeCell ref="D43:D45"/>
+    <mergeCell ref="C43:C45"/>
+    <mergeCell ref="B43:B45"/>
+    <mergeCell ref="C38:C42"/>
+    <mergeCell ref="D38:D42"/>
+    <mergeCell ref="E36:E37"/>
+    <mergeCell ref="D36:D37"/>
+    <mergeCell ref="D34:D35"/>
+    <mergeCell ref="D30:D33"/>
+    <mergeCell ref="C30:C33"/>
+    <mergeCell ref="B30:B33"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="C34:C35"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B26:B29"/>
+    <mergeCell ref="C26:C29"/>
+    <mergeCell ref="D26:D29"/>
+    <mergeCell ref="E26:E29"/>
+    <mergeCell ref="E30:E33"/>
+    <mergeCell ref="E34:E35"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="G17:G19"/>
+    <mergeCell ref="D23:D25"/>
+    <mergeCell ref="C23:C25"/>
+    <mergeCell ref="B23:B25"/>
+    <mergeCell ref="G20:G22"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="F23:F25"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="E14:E16"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="E23:E25"/>
+    <mergeCell ref="E3:E4"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C14:C16"/>
+    <mergeCell ref="D14:D16"/>
+    <mergeCell ref="C11:C13"/>
+    <mergeCell ref="D11:D13"/>
+    <mergeCell ref="A61:A63"/>
+    <mergeCell ref="B8:B10"/>
+    <mergeCell ref="C8:C10"/>
+    <mergeCell ref="D8:D10"/>
+    <mergeCell ref="E8:E10"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="B14:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B20:B22"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="A38:A42"/>
+    <mergeCell ref="A43:A45"/>
+    <mergeCell ref="A46:A49"/>
+    <mergeCell ref="A50:A52"/>
+    <mergeCell ref="A53:A57"/>
+    <mergeCell ref="A58:A60"/>
+    <mergeCell ref="A20:A22"/>
+    <mergeCell ref="A23:A25"/>
+    <mergeCell ref="A26:A29"/>
+    <mergeCell ref="A30:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A5:A7"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A8:A10"/>
+    <mergeCell ref="A11:A13"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C5:C7"/>
+    <mergeCell ref="D5:D7"/>
+    <mergeCell ref="E5:E7"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>